--- a/samples/Sample_5_For_Individual_Two_Children.xlsx
+++ b/samples/Sample_5_For_Individual_Two_Children.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nikhil Shetty</t>
+          <t>Pranav Kulkarni</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meera Sharma</t>
+          <t>Pooja Bhat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>63</v>
@@ -1076,11 +1076,7 @@
           <t>Creative Writing</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1089,30 +1085,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Creative Writing</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1187,16 +1179,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1215,26 +1207,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fractions</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Word Problems</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1309,22 +1305,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
         <v>83</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
         <v>63</v>
@@ -1437,10 +1437,14 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Community Helpers</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -1451,28 +1455,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Community Helpers</t>
+          <t>Maps &amp; Directions</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
